--- a/Sample_run/1/student/cuongnvhe181200/TC5/GradeDetail.xlsx
+++ b/Sample_run/1/student/cuongnvhe181200/TC5/GradeDetail.xlsx
@@ -158,9 +158,6 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>SYN_SENT</x:t>
-  </x:si>
-  <x:si>
     <x:t>PASS</x:t>
   </x:si>
   <x:si>
@@ -200,10 +197,10 @@
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
-    <x:t>RST-ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RESET</x:t>
+    <x:t>RST, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Connection reset</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -933,7 +930,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R27"/>
+  <x:dimension ref="A1:R11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
@@ -947,7 +944,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="29.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1047,7 +1044,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
         <x:v>44</x:v>
@@ -1059,13 +1056,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>58426</x:v>
+        <x:v>35888</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:18">
@@ -1085,10 +1082,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
@@ -1100,28 +1097,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R3" s="3" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R3" s="3" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18">
@@ -1141,10 +1138,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
@@ -1156,28 +1153,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R4" s="3" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R4" s="3" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:18">
@@ -1197,13 +1194,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G5" s="0" t="s">
+      <x:c r="H5" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>56</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>44</x:v>
@@ -1212,28 +1209,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R5" s="3" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R5" s="3" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:18">
@@ -1253,10 +1250,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
@@ -1268,28 +1265,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R6" s="3" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R6" s="3" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
@@ -1309,13 +1306,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
         <x:v>45</x:v>
@@ -1324,28 +1321,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R7" s="3" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="L7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R7" s="3" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1365,10 +1362,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
@@ -1380,36 +1377,36 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R8" s="3" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R8" s="3" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:18">
       <x:c r="A9" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>17</x:v>
@@ -1439,7 +1436,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
         <x:v>44</x:v>
@@ -1451,21 +1448,21 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>35790</x:v>
+        <x:v>35862</x:v>
       </x:c>
       <x:c r="Q9" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="R9" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:18">
       <x:c r="A10" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>17</x:v>
@@ -1492,10 +1489,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
         <x:v>45</x:v>
@@ -1510,962 +1507,66 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>35790</x:v>
+        <x:v>35862</x:v>
       </x:c>
       <x:c r="R10" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:18">
       <x:c r="A11" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P11" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q11" s="0">
+        <x:v>35888</x:v>
+      </x:c>
+      <x:c r="R11" s="4" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="M11" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P11" s="0">
-        <x:v>35828</x:v>
-      </x:c>
-      <x:c r="Q11" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R11" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:18">
-      <x:c r="A12" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="M12" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P12" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q12" s="0">
-        <x:v>35828</x:v>
-      </x:c>
-      <x:c r="R12" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:18">
-      <x:c r="A13" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K13" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L13" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="M13" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="N13" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="O13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P13" s="0">
-        <x:v>53646</x:v>
-      </x:c>
-      <x:c r="Q13" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R13" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:18">
-      <x:c r="A14" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K14" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="L14" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="M14" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N14" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P14" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q14" s="0">
-        <x:v>53646</x:v>
-      </x:c>
-      <x:c r="R14" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:18">
-      <x:c r="A15" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K15" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L15" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="M15" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="N15" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="O15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P15" s="0">
-        <x:v>45788</x:v>
-      </x:c>
-      <x:c r="Q15" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R15" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:18">
-      <x:c r="A16" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K16" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="L16" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="M16" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N16" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P16" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q16" s="0">
-        <x:v>45788</x:v>
-      </x:c>
-      <x:c r="R16" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:18">
-      <x:c r="A17" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K17" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L17" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="M17" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="N17" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="O17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P17" s="0">
-        <x:v>54332</x:v>
-      </x:c>
-      <x:c r="Q17" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R17" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:18">
-      <x:c r="A18" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K18" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="L18" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="M18" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N18" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P18" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q18" s="0">
-        <x:v>54332</x:v>
-      </x:c>
-      <x:c r="R18" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:18">
-      <x:c r="A19" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K19" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L19" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="M19" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="N19" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="O19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P19" s="0">
-        <x:v>54348</x:v>
-      </x:c>
-      <x:c r="Q19" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R19" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:18">
-      <x:c r="A20" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C20" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F20" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G20" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H20" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I20" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J20" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K20" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="L20" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="M20" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N20" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O20" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P20" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q20" s="0">
-        <x:v>54348</x:v>
-      </x:c>
-      <x:c r="R20" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:18">
-      <x:c r="A21" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K21" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L21" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="M21" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="N21" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="O21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P21" s="0">
-        <x:v>49278</x:v>
-      </x:c>
-      <x:c r="Q21" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R21" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:18">
-      <x:c r="A22" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D22" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E22" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F22" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G22" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H22" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I22" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J22" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K22" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="L22" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="M22" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N22" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O22" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P22" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q22" s="0">
-        <x:v>49278</x:v>
-      </x:c>
-      <x:c r="R22" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:18">
-      <x:c r="A23" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K23" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L23" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="M23" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="N23" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="O23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P23" s="0">
-        <x:v>33160</x:v>
-      </x:c>
-      <x:c r="Q23" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R23" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:18">
-      <x:c r="A24" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K24" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="L24" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="M24" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N24" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P24" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q24" s="0">
-        <x:v>33160</x:v>
-      </x:c>
-      <x:c r="R24" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:18">
-      <x:c r="A25" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K25" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L25" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="M25" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="N25" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="O25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P25" s="0">
-        <x:v>58414</x:v>
-      </x:c>
-      <x:c r="Q25" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R25" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:18">
-      <x:c r="A26" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K26" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="L26" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="M26" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N26" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P26" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q26" s="0">
-        <x:v>58414</x:v>
-      </x:c>
-      <x:c r="R26" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:18">
-      <x:c r="A27" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E27" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F27" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G27" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H27" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I27" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J27" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K27" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="L27" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="M27" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N27" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O27" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P27" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q27" s="0">
-        <x:v>58426</x:v>
-      </x:c>
-      <x:c r="R27" s="4" t="s">
-        <x:v>59</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Sample_run/1/student/cuongnvhe181200/TC5/GradeDetail.xlsx
+++ b/Sample_run/1/student/cuongnvhe181200/TC5/GradeDetail.xlsx
@@ -1056,7 +1056,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>35888</x:v>
+        <x:v>45448</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1448,7 +1448,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>35862</x:v>
+        <x:v>45382</x:v>
       </x:c>
       <x:c r="Q9" s="0">
         <x:v>4000</x:v>
@@ -1507,7 +1507,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>35862</x:v>
+        <x:v>45382</x:v>
       </x:c>
       <x:c r="R10" s="4" t="s">
         <x:v>58</x:v>
@@ -1563,7 +1563,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>35888</x:v>
+        <x:v>45448</x:v>
       </x:c>
       <x:c r="R11" s="4" t="s">
         <x:v>58</x:v>
